--- a/thaco/color/1_DATA_Hours.xlsx
+++ b/thaco/color/1_DATA_Hours.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{293D5D53-C00F-844D-94E9-CACDBA7B4355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E8A519B-AD2E-B041-9284-267E3D8762D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40720" yWindow="500" windowWidth="28440" windowHeight="17560" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4161,7 +4161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>MSNV</t>
   </si>
@@ -4202,12 +4202,6 @@
     <t>PHSK work day</t>
   </si>
   <si>
-    <t>Truy thu theo QTT</t>
-  </si>
-  <si>
-    <t>Refund according to QTT</t>
-  </si>
-  <si>
     <t>First 14 days</t>
   </si>
   <si>
@@ -4223,9 +4217,6 @@
     <t>2006324</t>
   </si>
   <si>
-    <t>Realization part 1</t>
-  </si>
-  <si>
     <t>TT</t>
   </si>
 </sst>
@@ -4239,7 +4230,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4282,12 +4273,6 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
       <sz val="14"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -4341,7 +4326,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -4371,39 +4356,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -4418,122 +4370,109 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="1991-" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
@@ -4920,23 +4859,21 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="2" width="8.5" style="37" customWidth="1"/>
-    <col min="3" max="16" width="7.1640625" style="38" customWidth="1"/>
-    <col min="17" max="18" width="10.5" style="11" customWidth="1"/>
-    <col min="19" max="19" width="12.5" style="11" customWidth="1"/>
-    <col min="20" max="20" width="19.5" style="42" customWidth="1"/>
-    <col min="21" max="21" width="12.33203125" style="42" customWidth="1"/>
-    <col min="22" max="22" width="12.5" style="42" customWidth="1"/>
-    <col min="23" max="23" width="11.6640625" style="42" customWidth="1"/>
-    <col min="24" max="16384" width="9.1640625" style="42"/>
+    <col min="1" max="2" width="8.5" style="32" customWidth="1"/>
+    <col min="3" max="16" width="7.1640625" style="33" customWidth="1"/>
+    <col min="17" max="17" width="19.5" style="37" customWidth="1"/>
+    <col min="18" max="18" width="12.33203125" style="37" customWidth="1"/>
+    <col min="19" max="19" width="12.5" style="37" customWidth="1"/>
+    <col min="20" max="20" width="11.6640625" style="37" customWidth="1"/>
+    <col min="21" max="16384" width="9.1640625" style="37"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="6" customFormat="1" ht="54" customHeight="1" outlineLevel="1">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="54" customHeight="1" outlineLevel="1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -4975,648 +4912,588 @@
         <v>11</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>20</v>
-      </c>
     </row>
-    <row r="2" spans="1:24" s="12" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
-      <c r="A2" s="7">
+    <row r="2" spans="1:21" s="8" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="6">
         <v>2405236</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="7">
         <v>26</v>
       </c>
-      <c r="D2" s="9">
-        <v>0</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0</v>
-      </c>
-      <c r="F2" s="9">
-        <v>0</v>
-      </c>
-      <c r="G2" s="9">
-        <v>0</v>
-      </c>
-      <c r="H2" s="9">
-        <v>0</v>
-      </c>
-      <c r="I2" s="9">
-        <v>0</v>
-      </c>
-      <c r="J2" s="9">
-        <v>0</v>
-      </c>
-      <c r="K2" s="9">
-        <v>0</v>
-      </c>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9">
-        <v>0</v>
-      </c>
-      <c r="N2" s="9">
-        <v>0</v>
-      </c>
-      <c r="O2" s="9">
-        <v>0</v>
-      </c>
-      <c r="P2" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="11"/>
+      <c r="D2" s="7">
+        <v>0</v>
+      </c>
+      <c r="E2" s="7">
+        <v>0</v>
+      </c>
+      <c r="F2" s="7">
+        <v>0</v>
+      </c>
+      <c r="G2" s="7">
+        <v>0</v>
+      </c>
+      <c r="H2" s="7">
+        <v>0</v>
+      </c>
+      <c r="I2" s="7">
+        <v>0</v>
+      </c>
+      <c r="J2" s="7">
+        <v>0</v>
+      </c>
+      <c r="K2" s="7">
+        <v>0</v>
+      </c>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7">
+        <v>0</v>
+      </c>
+      <c r="N2" s="7">
+        <v>0</v>
+      </c>
+      <c r="O2" s="7">
+        <v>0</v>
+      </c>
+      <c r="P2" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:24" s="12" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
-      <c r="A3" s="7">
+    <row r="3" spans="1:21" s="8" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="6">
         <v>2106723</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="7">
         <v>19</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="7">
         <v>5</v>
       </c>
-      <c r="E3" s="9">
-        <v>0</v>
-      </c>
-      <c r="F3" s="9">
-        <v>0</v>
-      </c>
-      <c r="G3" s="9">
-        <v>0</v>
-      </c>
-      <c r="H3" s="9">
-        <v>0</v>
-      </c>
-      <c r="I3" s="9">
-        <v>0</v>
-      </c>
-      <c r="J3" s="9">
-        <v>0</v>
-      </c>
-      <c r="K3" s="9">
-        <v>0</v>
-      </c>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9">
-        <v>0</v>
-      </c>
-      <c r="N3" s="9">
-        <v>0</v>
-      </c>
-      <c r="O3" s="9">
-        <v>0</v>
-      </c>
-      <c r="P3" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="11"/>
+      <c r="E3" s="7">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7">
+        <v>0</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0</v>
+      </c>
+      <c r="H3" s="7">
+        <v>0</v>
+      </c>
+      <c r="I3" s="7">
+        <v>0</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0</v>
+      </c>
+      <c r="K3" s="7">
+        <v>0</v>
+      </c>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7">
+        <v>0</v>
+      </c>
+      <c r="N3" s="7">
+        <v>0</v>
+      </c>
+      <c r="O3" s="7">
+        <v>0</v>
+      </c>
+      <c r="P3" s="7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:24" s="12" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
-      <c r="A4" s="7">
+    <row r="4" spans="1:21" s="8" customFormat="1" ht="14" customHeight="1" outlineLevel="1">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="7">
+        <v>24</v>
+      </c>
+      <c r="D4" s="7">
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7">
+        <v>0</v>
+      </c>
+      <c r="I4" s="7">
+        <v>0</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0</v>
+      </c>
+      <c r="K4" s="7">
+        <v>0</v>
+      </c>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7">
+        <v>2</v>
+      </c>
+      <c r="N4" s="7">
+        <v>0</v>
+      </c>
+      <c r="O4" s="7">
+        <v>0</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" s="10" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6">
+        <v>2406198</v>
+      </c>
+      <c r="C5" s="7">
+        <v>23</v>
+      </c>
+      <c r="D5" s="7">
+        <v>3</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7">
+        <v>0</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0</v>
+      </c>
+      <c r="K5" s="7">
+        <v>0</v>
+      </c>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7">
+        <v>0</v>
+      </c>
+      <c r="N5" s="7">
+        <v>0</v>
+      </c>
+      <c r="O5" s="7">
+        <v>0</v>
+      </c>
+      <c r="P5" s="7">
+        <v>0</v>
+      </c>
+      <c r="T5" s="11"/>
+      <c r="U5" s="12"/>
+    </row>
+    <row r="6" spans="1:21" s="10" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="7">
+        <v>22</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0</v>
+      </c>
+      <c r="E6" s="7">
+        <v>2</v>
+      </c>
+      <c r="F6" s="7">
+        <v>2</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="7">
+        <v>0</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7">
+        <v>2</v>
+      </c>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7">
+        <v>0</v>
+      </c>
+      <c r="N6" s="7">
+        <v>0</v>
+      </c>
+      <c r="O6" s="7">
+        <v>0</v>
+      </c>
+      <c r="P6" s="7">
+        <v>0</v>
+      </c>
+      <c r="T6" s="11"/>
+      <c r="U6" s="12"/>
+    </row>
+    <row r="7" spans="1:21" s="13" customFormat="1" ht="19.25" customHeight="1">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6">
+        <v>2406145</v>
+      </c>
+      <c r="C7" s="7">
+        <v>26</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="7">
+        <v>0</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="7">
+        <v>0</v>
+      </c>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7">
+        <v>0</v>
+      </c>
+      <c r="N7" s="7">
+        <v>0</v>
+      </c>
+      <c r="O7" s="7">
+        <v>0</v>
+      </c>
+      <c r="P7" s="7">
+        <v>0</v>
+      </c>
+      <c r="T7" s="11"/>
+      <c r="U7" s="12"/>
+    </row>
+    <row r="8" spans="1:21" s="13" customFormat="1" ht="38.25" customHeight="1">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="9">
-        <v>24</v>
-      </c>
-      <c r="D4" s="9">
-        <v>0</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0</v>
-      </c>
-      <c r="F4" s="9">
-        <v>0</v>
-      </c>
-      <c r="G4" s="9">
-        <v>0</v>
-      </c>
-      <c r="H4" s="9">
-        <v>0</v>
-      </c>
-      <c r="I4" s="9">
-        <v>0</v>
-      </c>
-      <c r="J4" s="9">
-        <v>0</v>
-      </c>
-      <c r="K4" s="9">
-        <v>0</v>
-      </c>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9">
+      <c r="C8" s="7">
+        <v>26</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
+        <v>5</v>
+      </c>
+      <c r="I8" s="7">
         <v>2</v>
       </c>
-      <c r="N4" s="9">
-        <v>0</v>
-      </c>
-      <c r="O4" s="9">
-        <v>0</v>
-      </c>
-      <c r="P4" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="11"/>
+      <c r="J8" s="7">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7">
+        <v>0</v>
+      </c>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7">
+        <v>0</v>
+      </c>
+      <c r="N8" s="7">
+        <v>0</v>
+      </c>
+      <c r="O8" s="7">
+        <v>0</v>
+      </c>
+      <c r="P8" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="14"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="12"/>
     </row>
-    <row r="5" spans="1:24" s="14" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A5" s="7">
-        <v>4</v>
-      </c>
-      <c r="B5" s="8">
-        <v>2406198</v>
-      </c>
-      <c r="C5" s="9">
-        <v>23</v>
-      </c>
-      <c r="D5" s="9">
-        <v>3</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0</v>
-      </c>
-      <c r="F5" s="9">
-        <v>0</v>
-      </c>
-      <c r="G5" s="9">
-        <v>0</v>
-      </c>
-      <c r="H5" s="9">
-        <v>0</v>
-      </c>
-      <c r="I5" s="9">
-        <v>0</v>
-      </c>
-      <c r="J5" s="9">
-        <v>0</v>
-      </c>
-      <c r="K5" s="9">
-        <v>0</v>
-      </c>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9">
-        <v>0</v>
-      </c>
-      <c r="N5" s="9">
-        <v>0</v>
-      </c>
-      <c r="O5" s="9">
-        <v>0</v>
-      </c>
-      <c r="P5" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="11"/>
-      <c r="W5" s="15"/>
-      <c r="X5" s="16"/>
+    <row r="9" spans="1:21" s="23" customFormat="1" ht="18">
+      <c r="A9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="22"/>
     </row>
-    <row r="6" spans="1:24" s="14" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="9">
-        <v>22</v>
-      </c>
-      <c r="D6" s="9">
-        <v>0</v>
-      </c>
-      <c r="E6" s="9">
-        <v>2</v>
-      </c>
-      <c r="F6" s="9">
-        <v>2</v>
-      </c>
-      <c r="G6" s="9">
-        <v>0</v>
-      </c>
-      <c r="H6" s="9">
-        <v>0</v>
-      </c>
-      <c r="I6" s="9">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9">
-        <v>0</v>
-      </c>
-      <c r="K6" s="9">
-        <v>2</v>
-      </c>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9">
-        <v>0</v>
-      </c>
-      <c r="N6" s="9">
-        <v>0</v>
-      </c>
-      <c r="O6" s="9">
-        <v>0</v>
-      </c>
-      <c r="P6" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="11"/>
-      <c r="W6" s="15"/>
-      <c r="X6" s="16"/>
+    <row r="10" spans="1:21" s="23" customFormat="1" ht="20">
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="26"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="22"/>
     </row>
-    <row r="7" spans="1:24" s="17" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A7" s="7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="8">
-        <v>2406145</v>
-      </c>
-      <c r="C7" s="9">
-        <v>26</v>
-      </c>
-      <c r="D7" s="9">
-        <v>0</v>
-      </c>
-      <c r="E7" s="9">
-        <v>0</v>
-      </c>
-      <c r="F7" s="9">
-        <v>0</v>
-      </c>
-      <c r="G7" s="9">
-        <v>0</v>
-      </c>
-      <c r="H7" s="9">
-        <v>0</v>
-      </c>
-      <c r="I7" s="9">
-        <v>0</v>
-      </c>
-      <c r="J7" s="9">
-        <v>0</v>
-      </c>
-      <c r="K7" s="9">
-        <v>0</v>
-      </c>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9">
-        <v>0</v>
-      </c>
-      <c r="N7" s="9">
-        <v>0</v>
-      </c>
-      <c r="O7" s="9">
-        <v>0</v>
-      </c>
-      <c r="P7" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="11"/>
-      <c r="W7" s="15"/>
-      <c r="X7" s="16"/>
+    <row r="11" spans="1:21" s="23" customFormat="1" ht="20">
+      <c r="A11" s="29"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="22"/>
     </row>
-    <row r="8" spans="1:24" s="17" customFormat="1" ht="38.25" customHeight="1">
-      <c r="A8" s="7">
-        <v>7</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="9">
-        <v>26</v>
-      </c>
-      <c r="D8" s="9">
-        <v>0</v>
-      </c>
-      <c r="E8" s="9">
-        <v>0</v>
-      </c>
-      <c r="F8" s="9">
-        <v>0</v>
-      </c>
-      <c r="G8" s="9">
-        <v>0</v>
-      </c>
-      <c r="H8" s="9">
-        <v>5</v>
-      </c>
-      <c r="I8" s="9">
-        <v>2</v>
-      </c>
-      <c r="J8" s="9">
-        <v>0</v>
-      </c>
-      <c r="K8" s="9">
-        <v>0</v>
-      </c>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9">
-        <v>0</v>
-      </c>
-      <c r="N8" s="9">
-        <v>0</v>
-      </c>
-      <c r="O8" s="9">
-        <v>0</v>
-      </c>
-      <c r="P8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="14"/>
-      <c r="U8" s="18"/>
-      <c r="W8" s="15"/>
-      <c r="X8" s="16"/>
+    <row r="12" spans="1:21" s="23" customFormat="1">
+      <c r="A12" s="32"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="33"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="22"/>
     </row>
-    <row r="9" spans="1:24" s="28" customFormat="1" ht="18">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="21"/>
-      <c r="N9" s="21"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
-      <c r="T9" s="24"/>
-      <c r="U9" s="25"/>
-      <c r="V9" s="25"/>
-      <c r="W9" s="26"/>
-      <c r="X9" s="27"/>
+    <row r="13" spans="1:21" s="23" customFormat="1">
+      <c r="A13" s="32"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="33"/>
+      <c r="M13" s="33"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="33"/>
+      <c r="P13" s="33"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="22"/>
     </row>
-    <row r="10" spans="1:24" s="28" customFormat="1" ht="20">
-      <c r="A10" s="29"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="24"/>
-      <c r="U10" s="25"/>
-      <c r="V10" s="25"/>
-      <c r="W10" s="26"/>
-      <c r="X10" s="27"/>
+    <row r="14" spans="1:21" s="23" customFormat="1">
+      <c r="A14" s="32"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="33"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="22"/>
     </row>
-    <row r="11" spans="1:24" s="28" customFormat="1" ht="20">
-      <c r="A11" s="34"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="31"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="32"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="31"/>
-      <c r="R11" s="31"/>
-      <c r="S11" s="31"/>
-      <c r="T11" s="24"/>
-      <c r="U11" s="25"/>
-      <c r="V11" s="25"/>
-      <c r="W11" s="26"/>
-      <c r="X11" s="27"/>
+    <row r="15" spans="1:21" s="23" customFormat="1">
+      <c r="A15" s="32"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="33"/>
+      <c r="N15" s="33"/>
+      <c r="O15" s="33"/>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="22"/>
     </row>
-    <row r="12" spans="1:24" s="28" customFormat="1">
-      <c r="A12" s="37"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="38"/>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="38"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="24"/>
-      <c r="U12" s="25"/>
-      <c r="V12" s="25"/>
-      <c r="W12" s="26"/>
-      <c r="X12" s="27"/>
+    <row r="16" spans="1:21" s="34" customFormat="1" ht="18">
+      <c r="A16" s="32"/>
+      <c r="B16" s="32"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="33"/>
+      <c r="R16" s="35"/>
     </row>
-    <row r="13" spans="1:24" s="28" customFormat="1">
-      <c r="A13" s="37"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="38"/>
-      <c r="P13" s="38"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="24"/>
-      <c r="U13" s="25"/>
-      <c r="V13" s="25"/>
-      <c r="W13" s="26"/>
-      <c r="X13" s="27"/>
+    <row r="17" spans="1:18" s="26" customFormat="1" ht="20">
+      <c r="A17" s="32"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="33"/>
+      <c r="P17" s="33"/>
     </row>
-    <row r="14" spans="1:24" s="28" customFormat="1">
-      <c r="A14" s="37"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="38"/>
-      <c r="K14" s="38"/>
-      <c r="L14" s="38"/>
-      <c r="M14" s="38"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="38"/>
-      <c r="P14" s="38"/>
-      <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="25"/>
-      <c r="V14" s="25"/>
-      <c r="W14" s="26"/>
-      <c r="X14" s="27"/>
-    </row>
-    <row r="15" spans="1:24" s="28" customFormat="1">
-      <c r="A15" s="37"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="38"/>
-      <c r="L15" s="38"/>
-      <c r="M15" s="38"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="38"/>
-      <c r="P15" s="38"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="24"/>
-      <c r="U15" s="25"/>
-      <c r="V15" s="25"/>
-      <c r="W15" s="26"/>
-      <c r="X15" s="27"/>
-    </row>
-    <row r="16" spans="1:24" s="39" customFormat="1" ht="18">
-      <c r="A16" s="37"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="38"/>
-      <c r="P16" s="38"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
-      <c r="U16" s="40"/>
-    </row>
-    <row r="17" spans="1:21" s="31" customFormat="1" ht="20">
-      <c r="A17" s="37"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="38"/>
-      <c r="P17" s="38"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
-    </row>
-    <row r="18" spans="1:21" s="31" customFormat="1" ht="20">
-      <c r="A18" s="37"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="38"/>
-      <c r="M18" s="38"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="38"/>
-      <c r="P18" s="38"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
-      <c r="S18" s="11"/>
-      <c r="U18" s="41"/>
+    <row r="18" spans="1:18" s="26" customFormat="1" ht="20">
+      <c r="A18" s="32"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="33"/>
+      <c r="R18" s="36"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A9:A1048576 B2:B1048576">
+    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="19"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9:A1048576 B2:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
